--- a/ADM25JS010/SPE Java Standard Delta Curriculum_v1.0.xlsx
+++ b/ADM25JS010/SPE Java Standard Delta Curriculum_v1.0.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{F29248E9-ED90-4EB8-B557-F19E3A68EEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87EB5649-E148-4010-A53F-F9D010A34A37}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2880" yWindow="2880" windowWidth="14400" windowHeight="8170" tabRatio="811" firstSheet="3" activeTab="4" xr2:uid="{AD271FCD-1124-452C-8EE3-FE619F9CD99B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="811" firstSheet="1" activeTab="4" xr2:uid="{AD271FCD-1124-452C-8EE3-FE619F9CD99B}"/>
   </bookViews>
   <sheets>
     <sheet name="About the Curriculum" sheetId="1" r:id="rId1"/>
@@ -3712,6 +3712,63 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3721,12 +3778,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3757,60 +3808,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3838,6 +3838,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3849,24 +3867,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4338,10 +4338,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="71" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="13" t="s">
@@ -4357,18 +4357,18 @@
         <v>26</v>
       </c>
       <c r="G2" s="14"/>
-      <c r="H2" s="70">
+      <c r="H2" s="87">
         <f>SUM(E2:E16)</f>
         <v>92</v>
       </c>
-      <c r="I2" s="73">
+      <c r="I2" s="90">
         <f>ROUND(H2/45,2)</f>
         <v>2.04</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="68"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="15" t="s">
         <v>27</v>
       </c>
@@ -4382,15 +4382,15 @@
         <v>26</v>
       </c>
       <c r="G3" s="16"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="74"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="91"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="68"/>
-      <c r="B4" s="82" t="s">
+      <c r="A4" s="74"/>
+      <c r="B4" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="79" t="s">
+      <c r="C4" s="71" t="s">
         <v>30</v>
       </c>
       <c r="D4" s="14" t="s">
@@ -4401,13 +4401,13 @@
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="74"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="91"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="68"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="80"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="14" t="s">
         <v>31</v>
       </c>
@@ -4418,15 +4418,15 @@
         <v>32</v>
       </c>
       <c r="G5" s="14"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="74"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="91"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="68"/>
-      <c r="B6" s="79" t="s">
+      <c r="A6" s="74"/>
+      <c r="B6" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="71" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -4437,13 +4437,13 @@
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="74"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="91"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="68"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="14" t="s">
         <v>31</v>
       </c>
@@ -4454,15 +4454,15 @@
         <v>32</v>
       </c>
       <c r="G7" s="14"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="74"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="91"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="68"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="71" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -4473,13 +4473,13 @@
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="71"/>
-      <c r="I8" s="74"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="91"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="68"/>
+      <c r="A9" s="74"/>
       <c r="B9" s="39"/>
-      <c r="C9" s="80"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="14" t="s">
         <v>31</v>
       </c>
@@ -4490,11 +4490,11 @@
         <v>32</v>
       </c>
       <c r="G9" s="14"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="74"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="91"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="68"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="39"/>
       <c r="C10" s="12" t="s">
         <v>37</v>
@@ -4507,11 +4507,11 @@
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="74"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="91"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="68"/>
+      <c r="A11" s="74"/>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
@@ -4526,15 +4526,15 @@
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="74"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="91"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="68"/>
-      <c r="B12" s="84" t="s">
+      <c r="A12" s="74"/>
+      <c r="B12" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="71" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -4545,13 +4545,13 @@
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="74"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="91"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="68"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="80"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="14" t="s">
         <v>31</v>
       </c>
@@ -4562,11 +4562,11 @@
         <v>32</v>
       </c>
       <c r="G13" s="14"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="74"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="91"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="68"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="12" t="s">
         <v>38</v>
       </c>
@@ -4581,11 +4581,11 @@
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="74"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="91"/>
     </row>
     <row r="15" spans="1:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15" s="68"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="19" t="s">
         <v>44</v>
       </c>
@@ -4602,11 +4602,11 @@
       <c r="G15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="71"/>
-      <c r="I15" s="74"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="91"/>
     </row>
     <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="69"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="33" t="s">
         <v>47</v>
       </c>
@@ -4621,17 +4621,17 @@
         <v>26</v>
       </c>
       <c r="G16" s="13"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="75"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="92"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="71" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="14" t="s">
@@ -4644,19 +4644,19 @@
         <v>32</v>
       </c>
       <c r="G17" s="14"/>
-      <c r="H17" s="70">
+      <c r="H17" s="87">
         <f>SUM(E17:E45)</f>
         <v>331</v>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="93">
         <f>ROUND(H17/45,2)</f>
         <v>7.36</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="68"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="14" t="s">
         <v>31</v>
       </c>
@@ -4667,15 +4667,15 @@
         <v>32</v>
       </c>
       <c r="G18" s="14"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="77"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="94"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="68"/>
-      <c r="B19" s="82" t="s">
+      <c r="A19" s="74"/>
+      <c r="B19" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="71" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="14" t="s">
@@ -4686,13 +4686,13 @@
       </c>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="77"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="94"/>
     </row>
     <row r="20" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="68"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="72"/>
       <c r="D20" s="14" t="s">
         <v>31</v>
       </c>
@@ -4703,15 +4703,15 @@
         <v>32</v>
       </c>
       <c r="G20" s="14"/>
-      <c r="H20" s="71"/>
-      <c r="I20" s="77"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="94"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="68"/>
-      <c r="B21" s="82" t="s">
+      <c r="A21" s="74"/>
+      <c r="B21" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="71" t="s">
         <v>56</v>
       </c>
       <c r="D21" s="16" t="s">
@@ -4722,13 +4722,13 @@
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="77"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="94"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="68"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="72"/>
       <c r="D22" s="14" t="s">
         <v>31</v>
       </c>
@@ -4739,11 +4739,11 @@
         <v>32</v>
       </c>
       <c r="G22" s="16"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="77"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="94"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="68"/>
+      <c r="A23" s="74"/>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
@@ -4758,11 +4758,11 @@
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="77"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="94"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="68"/>
+      <c r="A24" s="74"/>
       <c r="B24" s="14" t="s">
         <v>38</v>
       </c>
@@ -4777,11 +4777,11 @@
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="77"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="94"/>
     </row>
     <row r="25" spans="1:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="A25" s="68"/>
+      <c r="A25" s="74"/>
       <c r="B25" s="19" t="s">
         <v>59</v>
       </c>
@@ -4798,15 +4798,15 @@
       <c r="G25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="71"/>
-      <c r="I25" s="77"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="94"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="68"/>
-      <c r="B26" s="79" t="s">
+      <c r="A26" s="74"/>
+      <c r="B26" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="71" t="s">
         <v>62</v>
       </c>
       <c r="D26" s="14" t="s">
@@ -4817,13 +4817,13 @@
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="77"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="94"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="68"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="80"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="72"/>
       <c r="D27" s="14" t="s">
         <v>31</v>
       </c>
@@ -4834,15 +4834,15 @@
         <v>32</v>
       </c>
       <c r="G27" s="14"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="77"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="94"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="68"/>
-      <c r="B28" s="79" t="s">
+      <c r="A28" s="74"/>
+      <c r="B28" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="71" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="14" t="s">
@@ -4853,13 +4853,13 @@
       </c>
       <c r="F28" s="14"/>
       <c r="G28" s="14"/>
-      <c r="H28" s="71"/>
-      <c r="I28" s="77"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="94"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="68"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
+      <c r="A29" s="74"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="72"/>
       <c r="D29" s="14" t="s">
         <v>31</v>
       </c>
@@ -4870,15 +4870,15 @@
         <v>32</v>
       </c>
       <c r="G29" s="14"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="77"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="94"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="68"/>
-      <c r="B30" s="81" t="s">
+      <c r="A30" s="74"/>
+      <c r="B30" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="71" t="s">
         <v>66</v>
       </c>
       <c r="D30" s="14" t="s">
@@ -4889,13 +4889,13 @@
       </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="77"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="94"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="68"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="80"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="72"/>
       <c r="D31" s="14" t="s">
         <v>31</v>
       </c>
@@ -4906,11 +4906,11 @@
         <v>32</v>
       </c>
       <c r="G31" s="14"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="77"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="94"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="68"/>
+      <c r="A32" s="74"/>
       <c r="B32" s="14" t="s">
         <v>67</v>
       </c>
@@ -4927,11 +4927,11 @@
         <v>26</v>
       </c>
       <c r="G32" s="14"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="77"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="94"/>
     </row>
     <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="74"/>
       <c r="B33" s="14" t="s">
         <v>69</v>
       </c>
@@ -4948,11 +4948,11 @@
         <v>32</v>
       </c>
       <c r="G33" s="14"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="77"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="94"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="68"/>
+      <c r="A34" s="74"/>
       <c r="B34" s="14" t="s">
         <v>71</v>
       </c>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="77"/>
+      <c r="H34" s="88"/>
+      <c r="I34" s="94"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="68"/>
-      <c r="B35" s="82" t="s">
+      <c r="A35" s="74"/>
+      <c r="B35" s="64" t="s">
         <v>73</v>
       </c>
       <c r="C35" s="13" t="s">
@@ -4988,12 +4988,12 @@
         <v>26</v>
       </c>
       <c r="G35" s="14"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="77"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="94"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="68"/>
-      <c r="B36" s="83"/>
+      <c r="A36" s="74"/>
+      <c r="B36" s="82"/>
       <c r="C36" s="13" t="s">
         <v>76</v>
       </c>
@@ -5007,11 +5007,11 @@
         <v>26</v>
       </c>
       <c r="G36" s="14"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="77"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="94"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="68"/>
+      <c r="A37" s="74"/>
       <c r="B37" s="14" t="s">
         <v>77</v>
       </c>
@@ -5028,11 +5028,11 @@
         <v>26</v>
       </c>
       <c r="G37" s="14"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="77"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="94"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="68"/>
+      <c r="A38" s="74"/>
       <c r="B38" s="14" t="s">
         <v>79</v>
       </c>
@@ -5049,11 +5049,11 @@
         <v>32</v>
       </c>
       <c r="G38" s="14"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="77"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="94"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="68"/>
+      <c r="A39" s="74"/>
       <c r="B39" s="29" t="s">
         <v>38</v>
       </c>
@@ -5068,15 +5068,15 @@
       </c>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="77"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="94"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="68"/>
-      <c r="B40" s="82" t="s">
+      <c r="A40" s="74"/>
+      <c r="B40" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="71" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="14" t="s">
@@ -5087,13 +5087,13 @@
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="77"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="94"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="68"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="80"/>
+      <c r="A41" s="74"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="72"/>
       <c r="D41" s="14" t="s">
         <v>31</v>
       </c>
@@ -5104,11 +5104,11 @@
         <v>32</v>
       </c>
       <c r="G41" s="14"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="77"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="94"/>
     </row>
     <row r="42" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="68"/>
+      <c r="A42" s="74"/>
       <c r="B42" s="13" t="s">
         <v>84</v>
       </c>
@@ -5125,11 +5125,11 @@
         <v>86</v>
       </c>
       <c r="G42" s="14"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="77"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="94"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="68"/>
+      <c r="A43" s="74"/>
       <c r="B43" s="13" t="s">
         <v>87</v>
       </c>
@@ -5146,11 +5146,11 @@
         <v>26</v>
       </c>
       <c r="G43" s="14"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="77"/>
+      <c r="H43" s="88"/>
+      <c r="I43" s="94"/>
     </row>
     <row r="44" spans="1:9" ht="31" x14ac:dyDescent="0.35">
-      <c r="A44" s="68"/>
+      <c r="A44" s="74"/>
       <c r="B44" s="19" t="s">
         <v>89</v>
       </c>
@@ -5167,8 +5167,8 @@
       <c r="G44" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H44" s="71"/>
-      <c r="I44" s="77"/>
+      <c r="H44" s="88"/>
+      <c r="I44" s="94"/>
     </row>
     <row r="45" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A45" s="20"/>
@@ -5188,8 +5188,8 @@
       <c r="G45" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="71"/>
-      <c r="I45" s="77"/>
+      <c r="H45" s="88"/>
+      <c r="I45" s="94"/>
     </row>
     <row r="46" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="20"/>
@@ -5207,11 +5207,11 @@
         <v>32</v>
       </c>
       <c r="G46" s="32"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="78"/>
+      <c r="H46" s="89"/>
+      <c r="I46" s="95"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="83" t="s">
         <v>94</v>
       </c>
       <c r="B47" s="29" t="s">
@@ -5240,7 +5240,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="65"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="29" t="s">
         <v>98</v>
       </c>
@@ -5267,7 +5267,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="65"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="58" t="s">
         <v>100</v>
       </c>
@@ -5294,7 +5294,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A50" s="66"/>
+      <c r="A50" s="85"/>
       <c r="B50" s="29" t="s">
         <v>102</v>
       </c>
@@ -5340,23 +5340,23 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A52" s="89" t="s">
+      <c r="A52" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="90"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="90"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="90"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="90"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
     </row>
     <row r="53" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="91" t="s">
+      <c r="A53" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="B53" s="79" t="s">
+      <c r="B53" s="71" t="s">
         <v>106</v>
       </c>
       <c r="C53" s="13" t="s">
@@ -5365,29 +5365,51 @@
       <c r="D53" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E53" s="93"/>
-      <c r="F53" s="95"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="88"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="79"/>
+      <c r="G53" s="66"/>
+      <c r="H53" s="68"/>
+      <c r="I53" s="68"/>
     </row>
     <row r="54" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A54" s="92"/>
-      <c r="B54" s="80"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="72"/>
       <c r="C54" s="13" t="s">
         <v>108</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="94"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="H2:H16"/>
+    <mergeCell ref="I2:I16"/>
+    <mergeCell ref="H17:H46"/>
+    <mergeCell ref="I17:I46"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="G53:G54"/>
     <mergeCell ref="H53:H54"/>
@@ -5404,28 +5426,6 @@
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="H2:H16"/>
-    <mergeCell ref="I2:I16"/>
-    <mergeCell ref="H17:H46"/>
-    <mergeCell ref="I17:I46"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -5745,7 +5745,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="71" t="s">
         <v>155</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -5756,7 +5756,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="84"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="13" t="s">
         <v>158</v>
       </c>
@@ -5765,7 +5765,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="84"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="13" t="s">
         <v>160</v>
       </c>
@@ -5774,7 +5774,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A12" s="84"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="13" t="s">
         <v>162</v>
       </c>
@@ -5783,7 +5783,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="84"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="13" t="s">
         <v>164</v>
       </c>
@@ -5792,7 +5792,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="84"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="13" t="s">
         <v>166</v>
       </c>
@@ -5801,7 +5801,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="84"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="13" t="s">
         <v>168</v>
       </c>
@@ -5810,7 +5810,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A16" s="84"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="13" t="s">
         <v>170</v>
       </c>
@@ -5819,7 +5819,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="72"/>
       <c r="B17" s="13" t="s">
         <v>172</v>
       </c>
@@ -5828,7 +5828,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A18" s="79" t="s">
+      <c r="A18" s="71" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -5839,7 +5839,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A19" s="84"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="13" t="s">
         <v>177</v>
       </c>
@@ -5848,7 +5848,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="84"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="13" t="s">
         <v>179</v>
       </c>
@@ -5857,7 +5857,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A21" s="80"/>
+      <c r="A21" s="72"/>
       <c r="B21" s="13" t="s">
         <v>181</v>
       </c>
@@ -5866,7 +5866,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="71" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -5877,7 +5877,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A23" s="84"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="13" t="s">
         <v>184</v>
       </c>
@@ -5886,7 +5886,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="84"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="13" t="s">
         <v>186</v>
       </c>
@@ -5895,7 +5895,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="80"/>
+      <c r="A25" s="72"/>
       <c r="B25" s="13" t="s">
         <v>188</v>
       </c>
@@ -5904,7 +5904,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="79" t="s">
+      <c r="A26" s="71" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -5915,7 +5915,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="84"/>
+      <c r="A27" s="81"/>
       <c r="B27" s="13" t="s">
         <v>192</v>
       </c>
@@ -5924,7 +5924,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="84"/>
+      <c r="A28" s="81"/>
       <c r="B28" s="13" t="s">
         <v>194</v>
       </c>
@@ -5933,7 +5933,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="84"/>
+      <c r="A29" s="81"/>
       <c r="B29" s="13" t="s">
         <v>196</v>
       </c>
@@ -5942,7 +5942,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="84"/>
+      <c r="A30" s="81"/>
       <c r="B30" s="13" t="s">
         <v>198</v>
       </c>
@@ -5951,7 +5951,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="84"/>
+      <c r="A31" s="81"/>
       <c r="B31" s="13" t="s">
         <v>200</v>
       </c>
@@ -5960,7 +5960,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="79" t="s">
+      <c r="A32" s="71" t="s">
         <v>37</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -5971,7 +5971,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="84"/>
+      <c r="A33" s="81"/>
       <c r="B33" s="13" t="s">
         <v>204</v>
       </c>
@@ -5980,7 +5980,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="84"/>
+      <c r="A34" s="81"/>
       <c r="B34" s="13" t="s">
         <v>206</v>
       </c>
@@ -5989,7 +5989,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="80"/>
+      <c r="A35" s="72"/>
       <c r="B35" s="13" t="s">
         <v>208</v>
       </c>
@@ -5998,7 +5998,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="81" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -6009,7 +6009,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="290" x14ac:dyDescent="0.35">
-      <c r="A37" s="80"/>
+      <c r="A37" s="72"/>
       <c r="B37" s="13" t="s">
         <v>212</v>
       </c>
@@ -6152,7 +6152,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="106"/>
+      <c r="A12" s="112"/>
       <c r="B12" s="24" t="s">
         <v>235</v>
       </c>
@@ -6330,7 +6330,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="25" t="s">
         <v>273</v>
       </c>
@@ -6404,14 +6404,14 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="106"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="103"/>
       <c r="C40" s="22" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="109" t="s">
         <v>66</v>
       </c>
       <c r="B41" s="22" t="s">
@@ -6422,7 +6422,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A42" s="114"/>
+      <c r="A42" s="110"/>
       <c r="B42" s="21" t="s">
         <v>292</v>
       </c>
@@ -6431,7 +6431,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="116" x14ac:dyDescent="0.35">
-      <c r="A43" s="114"/>
+      <c r="A43" s="110"/>
       <c r="B43" s="21" t="s">
         <v>294</v>
       </c>
@@ -6440,7 +6440,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="114"/>
+      <c r="A44" s="110"/>
       <c r="B44" s="21" t="s">
         <v>296</v>
       </c>
@@ -6449,7 +6449,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="114"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="21" t="s">
         <v>298</v>
       </c>
@@ -6458,7 +6458,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="114"/>
+      <c r="A46" s="110"/>
       <c r="B46" s="21" t="s">
         <v>300</v>
       </c>
@@ -6467,7 +6467,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="114"/>
+      <c r="A47" s="110"/>
       <c r="B47" s="21" t="s">
         <v>302</v>
       </c>
@@ -6476,7 +6476,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="115"/>
+      <c r="A48" s="111"/>
       <c r="B48" s="21" t="s">
         <v>304</v>
       </c>
@@ -6485,7 +6485,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="107" t="s">
+      <c r="A49" s="113" t="s">
         <v>68</v>
       </c>
       <c r="B49" s="22" t="s">
@@ -6496,7 +6496,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A50" s="108"/>
+      <c r="A50" s="114"/>
       <c r="B50" s="22" t="s">
         <v>308</v>
       </c>
@@ -6505,7 +6505,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="108"/>
+      <c r="A51" s="114"/>
       <c r="B51" s="22" t="s">
         <v>310</v>
       </c>
@@ -6514,7 +6514,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="109"/>
+      <c r="A52" s="115"/>
       <c r="B52" s="22" t="s">
         <v>312</v>
       </c>
@@ -6626,7 +6626,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A64" s="106"/>
+      <c r="A64" s="112"/>
       <c r="B64" s="21" t="s">
         <v>336</v>
       </c>
@@ -6767,7 +6767,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="112"/>
       <c r="B79" s="22" t="s">
         <v>262</v>
       </c>
@@ -6877,7 +6877,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A91" s="106"/>
+      <c r="A91" s="112"/>
       <c r="B91" s="22" t="s">
         <v>390</v>
       </c>
@@ -6933,7 +6933,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="110" t="s">
+      <c r="A97" s="106" t="s">
         <v>88</v>
       </c>
       <c r="B97" s="22" t="s">
@@ -6944,7 +6944,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" ht="87" x14ac:dyDescent="0.35">
-      <c r="A98" s="111"/>
+      <c r="A98" s="107"/>
       <c r="B98" s="22" t="s">
         <v>404</v>
       </c>
@@ -6953,7 +6953,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="111"/>
+      <c r="A99" s="107"/>
       <c r="B99" s="22" t="s">
         <v>406</v>
       </c>
@@ -6962,7 +6962,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="111"/>
+      <c r="A100" s="107"/>
       <c r="B100" s="22" t="s">
         <v>408</v>
       </c>
@@ -6971,7 +6971,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="112"/>
+      <c r="A101" s="108"/>
       <c r="B101" s="29" t="s">
         <v>410</v>
       </c>
@@ -6981,6 +6981,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A29:A32"/>
     <mergeCell ref="B13:B17"/>
     <mergeCell ref="B38:B40"/>
     <mergeCell ref="A33:A36"/>
@@ -6994,12 +7000,6 @@
     <mergeCell ref="A70:A74"/>
     <mergeCell ref="A75:A79"/>
     <mergeCell ref="A80:A91"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A29:A32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7348,6 +7348,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D6E01E278A50734B8A721F01C1B19487" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1095c42701a8a0644b0e76b05dbde705">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="951c5514-b77c-4532-82d5-a05f2f7d58e2" xmlns:ns3="c6f516c4-2602-422c-aa9a-755893ba4f98" xmlns:ns4="3c35e321-f73a-4dae-ae38-a0459de24735" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5da9aabe1f17e52417e633868267d326" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
@@ -7613,27 +7633,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6f516c4-2602-422c-aa9a-755893ba4f98">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AEC7D5-CA6A-49AB-AC3C-62EA69A93819}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A35DFA12-810F-403D-9605-08880254932D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66DC9C7F-0C98-4B09-878A-7B81F39DCF3D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7651,23 +7670,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A35DFA12-810F-403D-9605-08880254932D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c6f516c4-2602-422c-aa9a-755893ba4f98"/>
-    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72AEC7D5-CA6A-49AB-AC3C-62EA69A93819}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>